--- a/proposals/2026-gangwon-meeting2/20261023_강원센터_제2차_집담회_참석기업_국유특허매칭.xlsx
+++ b/proposals/2026-gangwon-meeting2/20261023_강원센터_제2차_집담회_참석기업_국유특허매칭.xlsx
@@ -5797,9 +5797,9 @@
       <c r="O4" s="114" t="n"/>
       <c r="P4" s="143" t="inlineStr">
         <is>
-          <t>① 영상 또는 레이더 기반의 과수 형상 및 유무 판별을 통한 선택적 방제가 가능한 스마트 방제기 (등록 10-2336828) [적합도 상]
-② 풍향 및 풍속에 따라 측창 및 천창을 제어하는 스마트 온실 자동 제어 장치 및 그 방법 (등록 10-2675201) [적합도 상]
-③ 무인 병충해 방제 및 관수 장치 (등록 10-1570801) [적합도 중]</t>
+          <t>① 영상 또는 레이더 기반의 과수 형상 및 유무 판별을 통한 선택적 방제가 가능한 스마트 방제기 (등록 10-2336828)
+② 사물인터넷 기반의 온실 복합환경제어 플랫폼 (등록 10-3013389)
+③ 풍향 및 풍속에 따라 측창 및 천창을 제어하는 스마트 온실 자동 제어 장치 및 그 방법 (등록 10-2675201)</t>
         </is>
       </c>
     </row>
@@ -5849,9 +5849,9 @@
       <c r="O5" s="124" t="n"/>
       <c r="P5" s="144" t="inlineStr">
         <is>
-          <t>① 시설물의 시뮬레이션 방법 및 시스템 (등록 10-1980794) [적합도 상]
-② 클라우드 기반 실시간 온실 환경 의사결정지원 서버 및 시스템 (등록 10-2320987) [적합도 상]
-③ 작물의 종류에 따라 맞춤형 제어 정보를 사용자에게 제공할 수 있는 스마트 온실 시스템 및 그 방법 (등록 10-2586232) [적합도 중]</t>
+          <t>① 시설물의 시뮬레이션 방법 및 시스템 (등록 10-1980794) [AIS 종합 76점]
+② 클라우드 기반 실시간 온실 환경 의사결정지원 서버 및 이를 이용한 실시간 온실 환경 의사결정지원 시스템 (등록 10-2320987)
+③ 작물의 종류에 따라 맞춤형 제어 정보를 사용자에게 제공할 수 있는 스마트 온실 시스템 및 그 방법 (등록 10-2586232)</t>
         </is>
       </c>
     </row>
@@ -5901,9 +5901,9 @@
       <c r="O6" s="120" t="n"/>
       <c r="P6" s="145" t="inlineStr">
         <is>
-          <t>① 육질개선을 위한 가축용 사료첨가제 및 이의 제조방법 (등록 10-1352375) [적합도 상]
-② 비육후기 거세한우의 고온 스트레스 저감용 사료 첨가제 (출원 10-2023-0161394) [적합도 중]
-③ 조기 이유용 고에너지 사료 조성물 및 이를 이용한 근내지방도 개선 방법 (등록 10-1908725) [적합도 중]</t>
+          <t>① 비육후기 거세한우의 고온 스트레스 저감용 사료 첨가제 (등록 10-3013445)
+② 레스베라트롤(resveratrol)을 포함하는 면역 개선용 사료 첨가제 (등록 10-2964684)
+③ 돼지고기의 근내지방도 함량 예측용 바이오마커 및 그의 용도 (등록 10-2938518)</t>
         </is>
       </c>
     </row>
@@ -5953,9 +5953,9 @@
       <c r="O7" s="120" t="n"/>
       <c r="P7" s="145" t="inlineStr">
         <is>
-          <t>① 식물의 수액 유속 측정용 마이크로 니들 프로브 장치 및 이를 이용한 식물의 수액 유속 측정 방법 (등록 10-1920994) [적합도 하]
-② 소의 분만일 혈액 분석을 통한 케톤증 발생 위험개체 분류 방법 (등록 10-2800577) [적합도 하]
-③ 실시간 자동 유해 미생물 검출 장치 (등록 10-2134387) [적합도 하]</t>
+          <t>① 개의 당뇨 위험성 예측용 SNP 마커 및 이를 이용한 예측 방법 (등록 10-2194880)
+② 머신 러닝에 기반하여 소의 케톤증을 판별하는 장치 및 방법 (등록 10-3013571)
+③ 소의 분만일 혈액 분석을 통한 케톤증 발생 위험개체 분류 방법 (등록 10-2800577)</t>
         </is>
       </c>
     </row>
@@ -6005,9 +6005,9 @@
       <c r="O8" s="122" t="n"/>
       <c r="P8" s="144" t="inlineStr">
         <is>
-          <t>① 과산화수소 내성 및 항산화능이 우수한 신규 유산균 및 이의 용도 (등록 10-2884174) [적합도 상]
-② 신생아 분변에서 분리한 내산소성 비피도박테리움 롱검 비피더스 유산균 및 이를 이용한 프로바이오틱 조성물 (등록 10-1250463) [적합도 중]
-③ 미생물을 이용한 인삼 및 삼채의 복합 발효 추출액 및 캡슐 제조방법 (등록 10-1755118) [적합도 중]</t>
+          <t>① 과산화수소 내성 및 항산화능이 우수한 신규 유산균 및 이의 용도 (등록 10-2884174)
+② 누룩을 이용한 발효 인삼의 제조 방법 및 이를 포함하는 항산화 조성물 (공개 10-2023-0081062)
+③ 신규 유산균 락토바실러스 플란타럼 KCC-34 균주 (등록 10-2141569)</t>
         </is>
       </c>
     </row>
@@ -6057,8 +6057,9 @@
       <c r="O9" s="123" t="n"/>
       <c r="P9" s="144" t="inlineStr">
         <is>
-          <t>① 버섯 균사체를 이용한 친환경 포장용 대체소재 제조방법 및 그의 용도 (등록 10-2862954) [적합도 하]
-② 식품의 부패 감지용 필름형 지시계 및 제조방법 (출원 10-2023-0186050) [적합도 하]</t>
+          <t>① 기능성 천연 조미료 및 그 제조방법 (등록 10-2113842) [AIS 종합 80점]
+② 큰느타리버섯 균사체를 포함하는 대체육의 제조방법 (공개 10-2025-0056694)
+③ 버섯 균사체를 이용한 친환경 포장용 대체소재 제조방법 및 그의 용도 (등록 10-2862954)</t>
         </is>
       </c>
     </row>
@@ -6108,9 +6109,9 @@
       <c r="O10" s="120" t="n"/>
       <c r="P10" s="145" t="inlineStr">
         <is>
-          <t>① 발효오디추출물을 함유하는 항산화용 조성물 (출원 10-2018-0157250) [적합도 중]
-② 오가피 열매 발효물을 함유하는 면역증진용 조성물 (출원 10-2022-0046163) [적합도 중]
-③ 온도 및 광질에 따라 색깔이 변하는 보존화의 제조 방법 (등록 10-1097756) [적합도 하]</t>
+          <t>① 리나린 함량이 증가된 국화 신품종 식물 (등록 10-3013385)
+② 플라보노이드 함량이 증가된 감귤잎 침출차의 제조방법 (등록 10-2988475)
+③ 울릉국화 추출물을 포함하는 염증성 질환의 예방 또는 치료용 조성물 (등록 10-2496754)</t>
         </is>
       </c>
     </row>
@@ -6160,10 +6161,9 @@
       <c r="O11" s="120" t="n"/>
       <c r="P11" s="145" t="inlineStr">
         <is>
-          <t>① 달마시안제충국 추출물 및 효과증진제를 포함하는 버섯파리 방제용 살충제 조성물 (등록 10-1882678) [적합도 상]
-② 달마시안제충국 추출물을 포함하는 버섯파리 방제용 살충제 조성물 (등록 10-1885083) [적합도 상]
-③ 식물생장조절 기능을 갖는 계피 추출 정제물, 이의 효율적 제조방법 및 이를 활용한 제초제, 식물생장조절제 및 첨가제 (등록 10-1642801) [적합도 중]
-④ 식물생장조절 기능을 갖는 개똥쑥 추출 정제물, 이의 효율적 제조방법 및 이를 활용한 제초제, 식물생장조절제 및 첨가제 (등록 10-1634294) [적합도 중]</t>
+          <t>① 목단피 추출물을 포함하는 살충용 조성물 및 이의 제조방법 (등록 10-2862964)
+② 상백피 주정 추출물 및 로즈마리 주정 추출물을 포함하는 식물병원균 방제용 조성물 및 이의 용도 (등록 10-2525967)
+③ 딜 오일을 유효성분으로 포함하는 살충제 조성물 (공개 10-2024-0151519)</t>
         </is>
       </c>
     </row>
@@ -6213,9 +6213,9 @@
       <c r="O12" s="120" t="n"/>
       <c r="P12" s="145" t="inlineStr">
         <is>
-          <t>① 산조인 추출물을 포함하는 항 스트레스 조성물 및 이의 제조방법 (등록 10-1071154) [적합도 상]
-② 수면 장애 개선용 발효조성물 및 이의 제조방법 (등록 10-2182738) [적합도 중]
-③ 항우울 또는 항불안 활성을 갖는 쥐오줌풀 어린잎 추출물을 함유하는 조성물 (등록 10-1929353) [적합도 중]</t>
+          <t>① 수면 장애 개선용 발효조성물 및 이의 제조방법 (등록 10-2182738) [AIS 종합 79점]
+② 아세토박터 오리지퍼멘턴스를 이용한 저온발효 대추 발효식초 제조방법 (등록 10-2334548)
+③ 보리를 포함하는 GABA 함유량이 높은 요구르트 제조용 조성물, 제조방법 및 이로 제조된 요구르트 (등록 10-2387269)</t>
         </is>
       </c>
     </row>
@@ -6265,9 +6265,9 @@
       <c r="O13" s="124" t="n"/>
       <c r="P13" s="145" t="inlineStr">
         <is>
-          <t>① 감귤착즙액 함유 악취 저감용 미생물제제의 제조방법 및 이에 따라 제조된 악취 저감용 미생물제제 (출원 10-2023-0140832) [적합도 상]
-② 축산 분뇨의 악취 물질을 저감시키기 위한 환경 개선제 (등록 10-1655782) [적합도 상]
-③ 축산분뇨의 악취 제거용 조성물, 이를 이용한 비료 및 그 제조방법 (등록 10-1229865) [적합도 중]</t>
+          <t>① 암모니아 악취 저감용 혼합 미생물제제 및 이의 제조방법 (등록 10-1854277) [AIS 종합 86점]
+② 암모니아 회수 및 악취 저감 장치 (등록 10-2951527)
+③ 아스퍼질러스 속 균주 및 리조푸스 속 균주의 혼합 배양 방법 (등록 10-2010844) [AIS 종합 79점]</t>
         </is>
       </c>
     </row>
@@ -6317,9 +6317,9 @@
       <c r="O14" s="126" t="n"/>
       <c r="P14" s="145" t="inlineStr">
         <is>
-          <t>① 식품 원료를 이용한 반려동물용 수제 사료 조성물 및 이의 제조 방법 (등록 10-1855663) [적합도 중]
-② 기능성 개 사료용 조성물 및 이의 제조방법 (등록 10-1771973) [적합도 중]
-③ 반려견 사료 안전성 및 효능 평가를 위한 미세유체소자 기반 공배양 시스템 (등록 10-2939867) [적합도 중]</t>
+          <t>① 반려동물의 성장 단계에 따른 소화율을 이용하는 방법 (등록 10-2884168)
+② 흑염소 고기를 포함하는 장건강 개선용 사료조성물 및 이의 용도 (등록 10-2839139)
+③ 노루궁뎅이버섯 분말을 포함하는 항염증용 사료조성물 및 이의 용도 (등록 10-2941624)</t>
         </is>
       </c>
     </row>
@@ -6369,9 +6369,9 @@
       <c r="O15" s="120" t="n"/>
       <c r="P15" s="145" t="inlineStr">
         <is>
-          <t>① 행잉베드 농작물 수확용 전동대차 (등록 10-1980811) [적합도 상]
-② 온실의 다양한 레일 간격에 적용 가능한 이송 장치 및 이를 포함하는 농업용 작업 장치 (등록 10-2820148) [적합도 상]
-③ 추종이 가능한 자율주행 로봇, 로봇의 경로 추종 시스템 및 방법 (등록 10-2938283) [적합도 중]</t>
+          <t>① 행잉베드 농작물 수확용 전동대차 (등록 10-1980811) [AIS 종합 72점]
+② 온실의 다양한 레일 간격에 적용 가능한 이송 장치 및 이를 포함하는 농업용 작업 장치 (등록 10-2820148)
+③ 추종이 가능한 자율주행 로봇, 로봇의 경로 추종 시스템 및 방법 (등록 10-2938283)</t>
         </is>
       </c>
     </row>

--- a/proposals/2026-gangwon-meeting2/20261023_강원센터_제2차_집담회_참석기업_국유특허매칭.xlsx
+++ b/proposals/2026-gangwon-meeting2/20261023_강원센터_제2차_집담회_참석기업_국유특허매칭.xlsx
@@ -5797,9 +5797,9 @@
       <c r="O4" s="114" t="n"/>
       <c r="P4" s="143" t="inlineStr">
         <is>
-          <t>① 영상 또는 레이더 기반의 과수 형상 및 유무 판별을 통한 선택적 방제가 가능한 스마트 방제기 (등록 10-2336828)
-② 사물인터넷 기반의 온실 복합환경제어 플랫폼 (등록 10-3013389)
-③ 풍향 및 풍속에 따라 측창 및 천창을 제어하는 스마트 온실 자동 제어 장치 및 그 방법 (등록 10-2675201)</t>
+          <t>① 영상 또는 레이더 기반의 과수 형상 및 유무 판별을 통한 선택적 방제가 가능한 스마트 방제기 (등록 10-2336828) [AIS 종합 86점]
+② 사물인터넷 기반의 온실 복합환경제어 플랫폼 (등록 10-3013389) [AIS 종합 82점]
+③ 풍향 및 풍속에 따라 측창 및 천창을 제어하는 스마트 온실 자동 제어 장치 및 그 방법 (등록 10-2675201) [AIS 종합 88점]</t>
         </is>
       </c>
     </row>
@@ -5850,8 +5850,8 @@
       <c r="P5" s="144" t="inlineStr">
         <is>
           <t>① 시설물의 시뮬레이션 방법 및 시스템 (등록 10-1980794) [AIS 종합 76점]
-② 클라우드 기반 실시간 온실 환경 의사결정지원 서버 및 이를 이용한 실시간 온실 환경 의사결정지원 시스템 (등록 10-2320987)
-③ 작물의 종류에 따라 맞춤형 제어 정보를 사용자에게 제공할 수 있는 스마트 온실 시스템 및 그 방법 (등록 10-2586232)</t>
+② 클라우드 기반 실시간 온실 환경 의사결정지원 서버 및 이를 이용한 실시간 온실 환경 의사결정지원 시스템 (등록 10-2320987) [AIS 종합 88점]
+③ 작물의 종류에 따라 맞춤형 제어 정보를 사용자에게 제공할 수 있는 스마트 온실 시스템 및 그 방법 (등록 10-2586232) [AIS 종합 84점]</t>
         </is>
       </c>
     </row>
@@ -5901,9 +5901,9 @@
       <c r="O6" s="120" t="n"/>
       <c r="P6" s="145" t="inlineStr">
         <is>
-          <t>① 비육후기 거세한우의 고온 스트레스 저감용 사료 첨가제 (등록 10-3013445)
-② 레스베라트롤(resveratrol)을 포함하는 면역 개선용 사료 첨가제 (등록 10-2964684)
-③ 돼지고기의 근내지방도 함량 예측용 바이오마커 및 그의 용도 (등록 10-2938518)</t>
+          <t>① 비육후기 거세한우의 고온 스트레스 저감용 사료 첨가제 (등록 10-3013445) [AIS 종합 73점]
+② 레스베라트롤(resveratrol)을 포함하는 면역 개선용 사료 첨가제 (등록 10-2964684) [AIS 종합 77점]
+③ 돼지고기의 근내지방도 함량 예측용 바이오마커 및 그의 용도 (등록 10-2938518) [AIS 종합 74점]</t>
         </is>
       </c>
     </row>
@@ -5953,9 +5953,9 @@
       <c r="O7" s="120" t="n"/>
       <c r="P7" s="145" t="inlineStr">
         <is>
-          <t>① 개의 당뇨 위험성 예측용 SNP 마커 및 이를 이용한 예측 방법 (등록 10-2194880)
-② 머신 러닝에 기반하여 소의 케톤증을 판별하는 장치 및 방법 (등록 10-3013571)
-③ 소의 분만일 혈액 분석을 통한 케톤증 발생 위험개체 분류 방법 (등록 10-2800577)</t>
+          <t>① 개의 당뇨 위험성 예측용 SNP 마커 및 이를 이용한 예측 방법 (등록 10-2194880) [AIS 종합 71점]
+② 머신 러닝에 기반하여 소의 케톤증을 판별하는 장치 및 방법 (등록 10-3013571) [AIS 종합 85점]
+③ 소의 분만일 혈액 분석을 통한 케톤증 발생 위험개체 분류 방법 (등록 10-2800577) [AIS 종합 75점]</t>
         </is>
       </c>
     </row>
@@ -6005,9 +6005,9 @@
       <c r="O8" s="122" t="n"/>
       <c r="P8" s="144" t="inlineStr">
         <is>
-          <t>① 과산화수소 내성 및 항산화능이 우수한 신규 유산균 및 이의 용도 (등록 10-2884174)
-② 누룩을 이용한 발효 인삼의 제조 방법 및 이를 포함하는 항산화 조성물 (공개 10-2023-0081062)
-③ 신규 유산균 락토바실러스 플란타럼 KCC-34 균주 (등록 10-2141569)</t>
+          <t>① 과산화수소 내성 및 항산화능이 우수한 신규 유산균 및 이의 용도 (등록 10-2884174) [AIS 종합 91점]
+② 누룩을 이용한 발효 인삼의 제조 방법 및 이를 포함하는 항산화 조성물 (공개 10-2023-0081062) [AIS 종합 90점]
+③ 신규 유산균 락토바실러스 플란타럼 KCC-34 균주 (등록 10-2141569) [AIS 종합 83점]</t>
         </is>
       </c>
     </row>
@@ -6058,8 +6058,8 @@
       <c r="P9" s="144" t="inlineStr">
         <is>
           <t>① 기능성 천연 조미료 및 그 제조방법 (등록 10-2113842) [AIS 종합 80점]
-② 큰느타리버섯 균사체를 포함하는 대체육의 제조방법 (공개 10-2025-0056694)
-③ 버섯 균사체를 이용한 친환경 포장용 대체소재 제조방법 및 그의 용도 (등록 10-2862954)</t>
+② 큰느타리버섯 균사체를 포함하는 대체육의 제조방법 (공개 10-2025-0056694) [AIS 종합 77점]
+③ 버섯 균사체를 이용한 친환경 포장용 대체소재 제조방법 및 그의 용도 (등록 10-2862954) [AIS 종합 82점]</t>
         </is>
       </c>
     </row>
@@ -6109,9 +6109,9 @@
       <c r="O10" s="120" t="n"/>
       <c r="P10" s="145" t="inlineStr">
         <is>
-          <t>① 리나린 함량이 증가된 국화 신품종 식물 (등록 10-3013385)
-② 플라보노이드 함량이 증가된 감귤잎 침출차의 제조방법 (등록 10-2988475)
-③ 울릉국화 추출물을 포함하는 염증성 질환의 예방 또는 치료용 조성물 (등록 10-2496754)</t>
+          <t>① 리나린 함량이 증가된 국화 신품종 식물 (등록 10-3013385) [AIS 종합 84점]
+② 플라보노이드 함량이 증가된 감귤잎 침출차의 제조방법 (등록 10-2988475) [AIS 종합 79점]
+③ 울릉국화 추출물을 포함하는 염증성 질환의 예방 또는 치료용 조성물 (등록 10-2496754) [AIS 종합 82점]</t>
         </is>
       </c>
     </row>
@@ -6161,9 +6161,9 @@
       <c r="O11" s="120" t="n"/>
       <c r="P11" s="145" t="inlineStr">
         <is>
-          <t>① 목단피 추출물을 포함하는 살충용 조성물 및 이의 제조방법 (등록 10-2862964)
-② 상백피 주정 추출물 및 로즈마리 주정 추출물을 포함하는 식물병원균 방제용 조성물 및 이의 용도 (등록 10-2525967)
-③ 딜 오일을 유효성분으로 포함하는 살충제 조성물 (공개 10-2024-0151519)</t>
+          <t>① 목단피 추출물을 포함하는 살충용 조성물 및 이의 제조방법 (등록 10-2862964) [AIS 종합 75점]
+② 상백피 주정 추출물 및 로즈마리 주정 추출물을 포함하는 식물병원균 방제용 조성물 및 이의 용도 (등록 10-2525967) [AIS 종합 71점]
+③ 딜 오일을 유효성분으로 포함하는 살충제 조성물 (공개 10-2024-0151519) [AIS 종합 86점]</t>
         </is>
       </c>
     </row>
@@ -6214,8 +6214,8 @@
       <c r="P12" s="145" t="inlineStr">
         <is>
           <t>① 수면 장애 개선용 발효조성물 및 이의 제조방법 (등록 10-2182738) [AIS 종합 79점]
-② 아세토박터 오리지퍼멘턴스를 이용한 저온발효 대추 발효식초 제조방법 (등록 10-2334548)
-③ 보리를 포함하는 GABA 함유량이 높은 요구르트 제조용 조성물, 제조방법 및 이로 제조된 요구르트 (등록 10-2387269)</t>
+② 아세토박터 오리지퍼멘턴스를 이용한 저온발효 대추 발효식초 제조방법 (등록 10-2334548) [AIS 종합 75점]
+③ 보리를 포함하는 GABA 함유량이 높은 요구르트 제조용 조성물, 제조방법 및 이로 제조된 요구르트 (등록 10-2387269) [AIS 종합 77점]</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       <c r="P13" s="145" t="inlineStr">
         <is>
           <t>① 암모니아 악취 저감용 혼합 미생물제제 및 이의 제조방법 (등록 10-1854277) [AIS 종합 86점]
-② 암모니아 회수 및 악취 저감 장치 (등록 10-2951527)
+② 암모니아 회수 및 악취 저감 장치 (등록 10-2951527) [AIS 종합 79점]
 ③ 아스퍼질러스 속 균주 및 리조푸스 속 균주의 혼합 배양 방법 (등록 10-2010844) [AIS 종합 79점]</t>
         </is>
       </c>
@@ -6317,9 +6317,9 @@
       <c r="O14" s="126" t="n"/>
       <c r="P14" s="145" t="inlineStr">
         <is>
-          <t>① 반려동물의 성장 단계에 따른 소화율을 이용하는 방법 (등록 10-2884168)
-② 흑염소 고기를 포함하는 장건강 개선용 사료조성물 및 이의 용도 (등록 10-2839139)
-③ 노루궁뎅이버섯 분말을 포함하는 항염증용 사료조성물 및 이의 용도 (등록 10-2941624)</t>
+          <t>① 반려동물의 성장 단계에 따른 소화율을 이용하는 방법 (등록 10-2884168) [AIS 종합 86점]
+② 흑염소 고기를 포함하는 장건강 개선용 사료조성물 및 이의 용도 (등록 10-2839139) [AIS 종합 80점]
+③ 노루궁뎅이버섯 분말을 포함하는 항염증용 사료조성물 및 이의 용도 (등록 10-2941624) [AIS 종합 80점]</t>
         </is>
       </c>
     </row>
@@ -6370,8 +6370,8 @@
       <c r="P15" s="145" t="inlineStr">
         <is>
           <t>① 행잉베드 농작물 수확용 전동대차 (등록 10-1980811) [AIS 종합 72점]
-② 온실의 다양한 레일 간격에 적용 가능한 이송 장치 및 이를 포함하는 농업용 작업 장치 (등록 10-2820148)
-③ 추종이 가능한 자율주행 로봇, 로봇의 경로 추종 시스템 및 방법 (등록 10-2938283)</t>
+② 온실의 다양한 레일 간격에 적용 가능한 이송 장치 및 이를 포함하는 농업용 작업 장치 (등록 10-2820148) [AIS 종합 77점]
+③ 추종이 가능한 자율주행 로봇, 로봇의 경로 추종 시스템 및 방법 (등록 10-2938283) [AIS 종합 86점]</t>
         </is>
       </c>
     </row>
